--- a/decks/rally-corp/keyword-research.xlsx
+++ b/decks/rally-corp/keyword-research.xlsx
@@ -984,28 +984,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Donor Management Software: How Modern Nonprofits Win on Mobile</t>
+          <t>Fundraising Ideas For Kindergarteners: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>donor management software</t>
+          <t>fundraising ideas for kindergarteners</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>11</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1028,19 +1028,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fundraising Ideas For Kindergarteners: 25+ Real Examples Nonprofits Use</t>
+          <t>Bake Sale Fundraiser: Proven Ways Nonprofits Raise More</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for kindergarteners</t>
+          <t>bake sale fundraiser</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
         <v>2400</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bake Sale Fundraiser: Proven Ways Nonprofits Raise More</t>
+          <t>School Fundraisers: Proven Ways Nonprofits Raise More</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>bake sale fundraiser</t>
+          <t>school fundraisers</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
         <v>2400</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>26</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1116,19 +1116,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>School Fundraisers: Proven Ways Nonprofits Raise More</t>
+          <t>Fundraising Ideas For Nonprofits: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>school fundraisers</t>
+          <t>fundraising ideas for nonprofits</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
         <v>2400</v>
       </c>
       <c r="E13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1160,28 +1160,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fundraising Ideas For Nonprofits: 25+ Real Examples Nonprofits Use</t>
+          <t>Peer to Peer Fundraising: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for nonprofits</t>
+          <t>peer to peer fundraising</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
         <v>2400</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+        <v>45</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1204,33 +1204,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Peer to Peer Fundraising: How Modern Nonprofits Win on Mobile</t>
+          <t>Marketing Activities For a Charity Run: Proven Ways Nonprofits Raise More</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>peer to peer fundraising</t>
+          <t>marketing activities for a charity run</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>19</v>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1248,19 +1248,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Marketing Activities For a Charity Run: Proven Ways Nonprofits Raise More</t>
+          <t>Raffle Prizes: Proven Ways Nonprofits Raise More</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>marketing activities for a charity run</t>
+          <t>raffle prizes</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital Campaign: Proven Ways Nonprofits Raise More</t>
+          <t>Religious Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>capital campaign</t>
+          <t>religious fundraising ideas</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1336,28 +1336,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Religious Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
+          <t>Companies That Donate to Nonprofits: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>religious fundraising ideas</t>
+          <t>companies that donate to nonprofits</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1380,28 +1380,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Companies That Donate to Nonprofits: How Modern Nonprofits Win on Mobile</t>
+          <t>Thank You For Your Donation: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>companies that donate to nonprofits</t>
+          <t>thank you for your donation</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>17</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1424,28 +1424,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Donor Databases For Nonprofits: How Modern Nonprofits Win on Mobile</t>
+          <t>Tithely Church Login: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>donor databases for nonprofits</t>
+          <t>tithely church login</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="E20" t="n">
-        <v>46</v>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>32</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1468,23 +1468,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tithely Church Login: A Faith-Driven Fundraising Playbook</t>
+          <t>Tithe And Offering: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>tithely church login</t>
+          <t>tithe and offering</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="E21" t="n">
-        <v>32</v>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>40</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1512,28 +1512,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tithe And Offering: A Faith-Driven Fundraising Playbook</t>
+          <t>Mass Text App: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>tithe and offering</t>
+          <t>mass text app</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1556,23 +1556,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Church Donation: A Faith-Driven Fundraising Playbook</t>
+          <t>Church Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>church donation</t>
+          <t>church fundraising ideas</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="E23" t="n">
-        <v>46</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>14</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -1600,28 +1600,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thank You For Your Donation: A Practical Guide for Nonprofit Teams</t>
+          <t>Free Mass Texting App: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>thank you for your donation</t>
+          <t>free mass texting app</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1300</v>
+        <v>880</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>28</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1644,23 +1644,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mass Text App: How Modern Nonprofits Win on Mobile</t>
+          <t>Businesses That Donate to Nonprofits: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>mass text app</t>
+          <t>businesses that donate to nonprofits</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>29</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1688,23 +1688,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nonprofit Websites: How Modern Nonprofits Win on Mobile</t>
+          <t>Donation Request Letter: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>nonprofit websites</t>
+          <t>donation request letter</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="E26" t="n">
-        <v>45</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>34</v>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -1732,28 +1732,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Church Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
+          <t>990 Forms For Nonprofits: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>church fundraising ideas</t>
+          <t>990 forms for nonprofits</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>47</v>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1776,23 +1776,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Free Mass Texting App: How Modern Nonprofits Win on Mobile</t>
+          <t>Short Donation Messages Examples: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>free mass texting app</t>
+          <t>short donation messages examples</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>880</v>
+        <v>720</v>
       </c>
       <c r="E28" t="n">
-        <v>28</v>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>14</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -1820,23 +1820,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Businesses That Donate to Nonprofits: How Modern Nonprofits Win on Mobile</t>
+          <t>Corporations That Donate to Nonprofits: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>businesses that donate to nonprofits</t>
+          <t>corporations that donate to nonprofits</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>880</v>
+        <v>720</v>
       </c>
       <c r="E29" t="n">
-        <v>29</v>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>20</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1864,28 +1864,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Donation Request Letter: How Modern Nonprofits Win on Mobile</t>
+          <t>Tithe ly Login: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>donation request letter</t>
+          <t>tithe ly login</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>880</v>
+        <v>720</v>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1908,23 +1908,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tithely App: A Faith-Driven Fundraising Playbook</t>
+          <t>Church Fundraisers: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>tithely app</t>
+          <t>church fundraisers</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>880</v>
+        <v>720</v>
       </c>
       <c r="E31" t="n">
-        <v>46</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>25</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1952,28 +1952,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>990 Forms For Nonprofits: A Practical Guide for Nonprofit Teams</t>
+          <t>How to Send Mass Text on Iphone Without Group Message: A Practical Walkthrough</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>990 forms for nonprofits</t>
+          <t>how to send mass text on iphone without group message</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>880</v>
+        <v>590</v>
       </c>
       <c r="E32" t="n">
-        <v>47</v>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>17</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1996,16 +1996,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Consulting For Nonprofit Organizations: A Practical Guide for Nonprofit Teams</t>
+          <t>Mass Texting Service Free: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>consulting for nonprofit organizations</t>
+          <t>mass texting service free</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>480</v>
+        <v>590</v>
       </c>
       <c r="E33" t="n">
         <v>22</v>
@@ -2015,9 +2015,9 @@
           <t>Easy</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2040,19 +2040,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Non Profit Consulting Firms: A Practical Guide for Nonprofit Teams</t>
+          <t>Consulting For Nonprofit Organizations: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>non profit consulting firms</t>
+          <t>consulting for nonprofit organizations</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
         <v>480</v>
       </c>
       <c r="E34" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2084,19 +2084,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Register Non Profit: A Practical Guide for Nonprofit Teams</t>
+          <t>Non Profit Consulting Firms: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>register non profit</t>
+          <t>non profit consulting firms</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
         <v>480</v>
       </c>
       <c r="E35" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
@@ -2128,23 +2128,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Non Profit Company: A Practical Guide for Nonprofit Teams</t>
+          <t>Register Non Profit: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>non profit company</t>
+          <t>register non profit</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
         <v>480</v>
       </c>
       <c r="E36" t="n">
-        <v>49</v>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>35</v>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2172,33 +2172,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sample Thank You Note For Donation: A Practical Guide for Nonprofit Teams</t>
+          <t>Tithely Admin Login: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>sample thank you note for donation</t>
+          <t>tithely admin login</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="E37" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2348,33 +2348,33 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nonprofit Organizations to Start: Proven Ways Nonprofits Raise More</t>
+          <t>Mass Texting Service For Nonprofits: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>nonprofit organizations to start</t>
+          <t>mass texting service for nonprofits</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1900</v>
+        <v>260</v>
       </c>
       <c r="E41" t="n">
-        <v>29</v>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+        <v>17</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2392,23 +2392,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Raffle Prizes: Proven Ways Nonprofits Raise More</t>
+          <t>Capital Campaign: Proven Ways Nonprofits Raise More</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>raffle prizes</t>
+          <t>capital campaign</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="E42" t="n">
-        <v>16</v>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>29</v>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -2436,23 +2436,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>How to Start a Fundraiser: A Practical Walkthrough</t>
+          <t>Nonprofit Organizations to Start: Proven Ways Nonprofits Raise More</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>how to start a fundraiser</t>
+          <t>nonprofit organizations to start</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1300</v>
+        <v>1900</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>29</v>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2480,19 +2480,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Basket Raffle: Proven Ways Nonprofits Raise More</t>
+          <t>How to Start a Fundraiser: A Practical Walkthrough</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>basket raffle</t>
+          <t>how to start a fundraiser</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fundraising Ideas For Sports Teams: 25+ Real Examples Nonprofits Use</t>
+          <t>Basket Raffle: Proven Ways Nonprofits Raise More</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for sports teams</t>
+          <t>basket raffle</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2568,19 +2568,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sports Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
+          <t>Fundraising Ideas For Sports Teams: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>sports fundraising ideas</t>
+          <t>fundraising ideas for sports teams</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="E46" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2612,19 +2612,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>How to Start a Nonprofit Organization With no Money: A Practical Walkthrough</t>
+          <t>Sports Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>how to start a nonprofit organization with no money</t>
+          <t>sports fundraising ideas</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2656,19 +2656,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Raffle Ideas: 25+ Real Examples Nonprofits Use</t>
+          <t>How to Start a Nonprofit Organization With no Money: A Practical Walkthrough</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>raffle ideas</t>
+          <t>how to start a nonprofit organization with no money</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="E48" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2700,19 +2700,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>How to Earn Money For a Nonprofit Organization: A Practical Walkthrough</t>
+          <t>Raffle Ideas: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>how to earn money for a nonprofit organization</t>
+          <t>raffle ideas</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
@@ -2744,23 +2744,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Creative Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
+          <t>How to Earn Money For a Nonprofit Organization: A Practical Walkthrough</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>creative fundraising ideas</t>
+          <t>how to earn money for a nonprofit organization</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="E50" t="n">
-        <v>26</v>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>20</v>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -2788,19 +2788,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mass Text Message Application: How Modern Nonprofits Win on Mobile</t>
+          <t>Donor Databases For Nonprofits: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>mass text message application</t>
+          <t>donor databases for nonprofits</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>880</v>
+        <v>1300</v>
       </c>
       <c r="E51" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2832,28 +2832,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nonprofit Discounts: How Modern Nonprofits Win on Mobile</t>
+          <t>Church Donation: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>nonprofit discounts</t>
+          <t>church donation</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>880</v>
+        <v>1300</v>
       </c>
       <c r="E52" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2876,38 +2876,38 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sample Letters Asking For Donations: How Modern Nonprofits Win on Mobile</t>
+          <t>Best Raffle Prizes: 2026 Vetted Picks for Mission-Driven Teams</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>sample letters asking for donations</t>
+          <t>best raffle prizes</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
         <v>880</v>
       </c>
       <c r="E53" t="n">
-        <v>38</v>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>6</v>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
@@ -2920,23 +2920,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Short Donation Messages Examples: 25+ Real Examples Nonprofits Use</t>
+          <t>Mass Text Message Application: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>short donation messages examples</t>
+          <t>mass text message application</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>37</v>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -2964,23 +2964,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Corporations That Donate to Nonprofits: How Modern Nonprofits Win on Mobile</t>
+          <t>Nonprofit Discounts: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>corporations that donate to nonprofits</t>
+          <t>nonprofit discounts</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="E55" t="n">
-        <v>20</v>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>37</v>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -3008,23 +3008,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Requesting For Donation: How Modern Nonprofits Win on Mobile</t>
+          <t>Sample Letters Asking For Donations: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>requesting for donation</t>
+          <t>sample letters asking for donations</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>38</v>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -3052,33 +3052,33 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Donation Causes: How Modern Nonprofits Win on Mobile</t>
+          <t>Tithely App: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>donation causes</t>
+          <t>tithely app</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="E57" t="n">
-        <v>34</v>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>46</v>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3096,19 +3096,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Free Mass Text Messaging App: How Modern Nonprofits Win on Mobile</t>
+          <t>Requesting For Donation: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>free mass text messaging app</t>
+          <t>requesting for donation</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
         <v>720</v>
       </c>
       <c r="E58" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
@@ -3140,33 +3140,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tithe ly Login: A Faith-Driven Fundraising Playbook</t>
+          <t>Donation Causes: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>tithe ly login</t>
+          <t>donation causes</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
         <v>720</v>
       </c>
       <c r="E59" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3184,28 +3184,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Church Fundraisers: A Faith-Driven Fundraising Playbook</t>
+          <t>How to Send Mass Text Messages: A Practical Walkthrough</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>church fundraisers</t>
+          <t>how to send mass text messages</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>720</v>
+        <v>590</v>
       </c>
       <c r="E60" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3228,23 +3228,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>How to Send Mass Text on Iphone Without Group Message: A Practical Walkthrough</t>
+          <t>Best Nonprofit Websites: 2026 Vetted Picks for Mission-Driven Teams</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>how to send mass text on iphone without group message</t>
+          <t>best nonprofit websites</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
         <v>590</v>
       </c>
       <c r="E61" t="n">
-        <v>17</v>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>25</v>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
@@ -3272,19 +3272,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mass Texting Service Free: How Modern Nonprofits Win on Mobile</t>
+          <t>Digital Marketing For Nonprofits: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>mass texting service free</t>
+          <t>digital marketing for nonprofits</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
         <v>590</v>
       </c>
       <c r="E62" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
@@ -3316,19 +3316,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>How to Send Mass Text Messages: A Practical Walkthrough</t>
+          <t>How to Ask For Donations: A Practical Walkthrough</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>how to send mass text messages</t>
+          <t>how to ask for donations</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
         <v>590</v>
       </c>
       <c r="E63" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
@@ -3360,23 +3360,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Best Nonprofit Websites: 2026 Vetted Picks for Mission-Driven Teams</t>
+          <t>Companies That Donate to Nonprofit Organizations: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>best nonprofit websites</t>
+          <t>companies that donate to nonprofit organizations</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>590</v>
+        <v>480</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>16</v>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
@@ -3404,23 +3404,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Digital Marketing For Nonprofits: How Modern Nonprofits Win on Mobile</t>
+          <t>Free Mass Text Messaging: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>digital marketing for nonprofits</t>
+          <t>free mass text messaging</t>
         </is>
       </c>
       <c r="D65" s="4" t="n">
-        <v>590</v>
+        <v>480</v>
       </c>
       <c r="E65" t="n">
-        <v>25</v>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>20</v>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3448,28 +3448,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tithely Admin Login: A Faith-Driven Fundraising Playbook</t>
+          <t>Donation x: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>tithely admin login</t>
+          <t>donation x</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="E66" t="n">
-        <v>21</v>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>13</v>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3492,38 +3492,38 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Best Church Management Software: 2026 Vetted Picks for Mission-Driven Teams</t>
+          <t>Sample Thank You Note For Donation: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>best church management software</t>
+          <t>sample thank you note for donation</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="E67" t="n">
-        <v>39</v>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G67" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>34</v>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
@@ -3624,23 +3624,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Crm Systems For Political Campaigns: A Practical Guide for Nonprofit Teams</t>
+          <t>Campaign Text: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>crm systems for political campaigns</t>
+          <t>campaign text</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
         <v>260</v>
       </c>
       <c r="E70" t="n">
-        <v>10</v>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>24</v>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3668,23 +3668,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mass Texting Service For Nonprofits: A Practical Guide for Nonprofit Teams</t>
+          <t>Nonprofit Conferences: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>mass texting service for nonprofits</t>
+          <t>nonprofit conferences</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
         <v>260</v>
       </c>
       <c r="E71" t="n">
-        <v>17</v>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>28</v>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3712,33 +3712,33 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Campaign Text: A Practical Guide for Nonprofit Teams</t>
+          <t>Church Texting: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>campaign text</t>
+          <t>church texting</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
         <v>260</v>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>19</v>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3756,33 +3756,33 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nonprofit Conferences: A Practical Guide for Nonprofit Teams</t>
+          <t>Fundraising Ideas For Church Building: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>nonprofit conferences</t>
+          <t>fundraising ideas for church building</t>
         </is>
       </c>
       <c r="D73" s="4" t="n">
         <v>260</v>
       </c>
       <c r="E73" t="n">
-        <v>28</v>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>20</v>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3800,23 +3800,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Messaging Platform: A Practical Guide for Nonprofit Teams</t>
+          <t>Crm Systems For Political Campaigns: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>messaging platform</t>
+          <t>crm systems for political campaigns</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
         <v>260</v>
       </c>
       <c r="E74" t="n">
-        <v>37</v>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>10</v>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4064,28 +4064,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fundraising Ideas For Students: 25+ Real Examples Nonprofits Use</t>
+          <t>Sms For Nonprofits: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for students</t>
+          <t>sms for nonprofits</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>1300</v>
+        <v>170</v>
       </c>
       <c r="E80" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -4108,28 +4108,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fundraising Ideas For Kids: 25+ Real Examples Nonprofits Use</t>
+          <t>Thank You For Generous Donation: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for kids</t>
+          <t>thank you for generous donation</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="E81" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -4152,28 +4152,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>College Nonprofit Ideas: 25+ Real Examples Nonprofits Use</t>
+          <t>Donor Management Software: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>college nonprofit ideas</t>
+          <t>donor management software</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>1000</v>
+        <v>2900</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
-      </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+        <v>54</v>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4196,23 +4196,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Raffle Prize Ideas: 25+ Real Examples Nonprofits Use</t>
+          <t>Creative Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>raffle prize ideas</t>
+          <t>creative fundraising ideas</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="E83" t="n">
-        <v>19</v>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>26</v>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Charity Event: Proven Ways Nonprofits Raise More</t>
+          <t>Fundraising Ideas For Students: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>charity event</t>
+          <t>fundraising ideas for students</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="E84" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -4284,23 +4284,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>High School Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
+          <t>Fundraising Ideas For Kids: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>high school fundraising ideas</t>
+          <t>fundraising ideas for kids</t>
         </is>
       </c>
       <c r="D85" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="E85" t="n">
-        <v>24</v>
-      </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>15</v>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
@@ -4328,23 +4328,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Charity Gala: Proven Ways Nonprofits Raise More</t>
+          <t>College Nonprofit Ideas: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>charity gala</t>
+          <t>college nonprofit ideas</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="E86" t="n">
-        <v>26</v>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>18</v>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4372,19 +4372,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Best Raffle Prizes: 2026 Vetted Picks for Mission-Driven Teams</t>
+          <t>Raffle Prize Ideas: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>best raffle prizes</t>
+          <t>raffle prize ideas</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="E87" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
@@ -4416,23 +4416,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>How do You Make Money With a Non Profit Organization: A Practical Walkthrough</t>
+          <t>Charity Event: Proven Ways Nonprofits Raise More</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>how do you make money with a non profit organization</t>
+          <t>charity event</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="E88" t="n">
-        <v>17</v>
-      </c>
-      <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>23</v>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -4460,23 +4460,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fundraising Ideas For Clubs: 25+ Real Examples Nonprofits Use</t>
+          <t>High School Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for clubs</t>
+          <t>high school fundraising ideas</t>
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="E89" t="n">
-        <v>18</v>
-      </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>24</v>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
@@ -4504,28 +4504,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>How to Ask For Donations: A Practical Walkthrough</t>
+          <t>Charity Gala: Proven Ways Nonprofits Raise More</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>how to ask for donations</t>
+          <t>charity gala</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>590</v>
+        <v>1000</v>
       </c>
       <c r="E90" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4548,23 +4548,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Best Texting Service For Business: 2026 Vetted Picks for Mission-Driven Teams</t>
+          <t>Nonprofit Websites: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>best texting service for business</t>
+          <t>nonprofit websites</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>590</v>
+        <v>1000</v>
       </c>
       <c r="E91" t="n">
-        <v>31</v>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>45</v>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
@@ -4592,28 +4592,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Short Code Texting: How Modern Nonprofits Win on Mobile</t>
+          <t>How do You Make Money With a Non Profit Organization: A Practical Walkthrough</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>short code texting</t>
+          <t>how do you make money with a non profit organization</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>590</v>
+        <v>880</v>
       </c>
       <c r="E92" t="n">
-        <v>35</v>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>17</v>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4636,28 +4636,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Companies That Donate to Nonprofit Organizations: How Modern Nonprofits Win on Mobile</t>
+          <t>Fundraising Ideas For Clubs: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>companies that donate to nonprofit organizations</t>
+          <t>fundraising ideas for clubs</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>480</v>
+        <v>880</v>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4680,23 +4680,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Free Mass Text Messaging: How Modern Nonprofits Win on Mobile</t>
+          <t>Free Mass Text Messaging App: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>free mass text messaging</t>
+          <t>free mass text messaging app</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="E94" t="n">
-        <v>20</v>
-      </c>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>35</v>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4724,19 +4724,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>How to Send a Mass Text on Iphone: A Practical Walkthrough</t>
+          <t>Best Texting Service For Business: 2026 Vetted Picks for Mission-Driven Teams</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>how to send a mass text on iphone</t>
+          <t>best texting service for business</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>480</v>
+        <v>590</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
@@ -4768,19 +4768,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Free Nonprofit Crm: How Modern Nonprofits Win on Mobile</t>
+          <t>Short Code Texting: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>free nonprofit crm</t>
+          <t>short code texting</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>480</v>
+        <v>590</v>
       </c>
       <c r="E96" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4812,19 +4812,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nonprofit Website Builder: How Modern Nonprofits Win on Mobile</t>
+          <t>How to Send a Mass Text on Iphone: A Practical Walkthrough</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>nonprofit website builder</t>
+          <t>how to send a mass text on iphone</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
         <v>480</v>
       </c>
       <c r="E97" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
@@ -4856,19 +4856,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Credit Card Processing For Nonprofits: How Modern Nonprofits Win on Mobile</t>
+          <t>Free Nonprofit Crm: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>credit card processing for nonprofits</t>
+          <t>free nonprofit crm</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
         <v>480</v>
       </c>
       <c r="E98" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
@@ -4900,23 +4900,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Donation x: How Modern Nonprofits Win on Mobile</t>
+          <t>Nonprofit Website Builder: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>donation x</t>
+          <t>nonprofit website builder</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="E99" t="n">
-        <v>13</v>
-      </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>27</v>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4944,23 +4944,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nonprofit it Support: How Modern Nonprofits Win on Mobile</t>
+          <t>Credit Card Processing For Nonprofits: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>nonprofit it support</t>
+          <t>credit card processing for nonprofits</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="E100" t="n">
-        <v>19</v>
-      </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>28</v>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4988,28 +4988,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>List of Companies Willing to Donate to Fundraisers: How Modern Nonprofits Win on Mobile</t>
+          <t>Non Profit Company: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>list of companies willing to donate to fundraisers</t>
+          <t>non profit company</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="E101" t="n">
-        <v>20</v>
-      </c>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>49</v>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5032,28 +5032,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Free Mass Texting: How Modern Nonprofits Win on Mobile</t>
+          <t>Best Church Management Software: 2026 Vetted Picks for Mission-Driven Teams</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>free mass texting</t>
+          <t>best church management software</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="E102" t="n">
-        <v>21</v>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>39</v>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
@@ -5076,19 +5076,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>How do You Send a Mass Text: A Practical Walkthrough</t>
+          <t>Nonprofit it Support: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>how do you send a mass text</t>
+          <t>nonprofit it support</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="E103" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5120,33 +5120,33 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Church Texting: A Faith-Driven Fundraising Playbook</t>
+          <t>List of Companies Willing to Donate to Fundraisers: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>church texting</t>
+          <t>list of companies willing to donate to fundraisers</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="E104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5164,33 +5164,33 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fundraising Ideas For Church Building: 25+ Real Examples Nonprofits Use</t>
+          <t>Free Mass Texting: How Modern Nonprofits Win on Mobile</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for church building</t>
+          <t>free mass texting</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="E105" t="n">
-        <v>20</v>
-      </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G105" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>21</v>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5208,28 +5208,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Small Church Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
+          <t>How do You Send a Mass Text: A Practical Walkthrough</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>small church fundraising ideas</t>
+          <t>how do you send a mass text</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="E106" t="n">
-        <v>23</v>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G106" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>14</v>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5252,28 +5252,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ideas to Raise Money For Church: 25+ Real Examples Nonprofits Use</t>
+          <t>Messaging Platform: A Practical Guide for Nonprofit Teams</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>ideas to raise money for church</t>
+          <t>messaging platform</t>
         </is>
       </c>
       <c r="D107" s="4" t="n">
         <v>260</v>
       </c>
       <c r="E107" t="n">
-        <v>28</v>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G107" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>37</v>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5296,23 +5296,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Text Messaging Service For Churches: A Faith-Driven Fundraising Playbook</t>
+          <t>Small Church Fundraising Ideas: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>text messaging service for churches</t>
+          <t>small church fundraising ideas</t>
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
-      </c>
-      <c r="F108" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>23</v>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5340,23 +5340,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fundraising Ideas For Church Youth Groups: 25+ Real Examples Nonprofits Use</t>
+          <t>Ideas to Raise Money For Church: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for church youth groups</t>
+          <t>ideas to raise money for church</t>
         </is>
       </c>
       <c r="D109" s="4" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="E109" t="n">
-        <v>13</v>
-      </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>28</v>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
@@ -5384,19 +5384,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Giving to The Church: A Faith-Driven Fundraising Playbook</t>
+          <t>Text Messaging Service For Churches: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>giving to the church</t>
+          <t>text messaging service for churches</t>
         </is>
       </c>
       <c r="D110" s="4" t="n">
         <v>210</v>
       </c>
       <c r="E110" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Youth Fundraising Ideas For Church: 25+ Real Examples Nonprofits Use</t>
+          <t>Fundraising Ideas For Church Youth Groups: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>youth fundraising ideas for church</t>
+          <t>fundraising ideas for church youth groups</t>
         </is>
       </c>
       <c r="D111" s="4" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="E111" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -5472,28 +5472,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sms For Nonprofits: A Practical Guide for Nonprofit Teams</t>
+          <t>Giving to The Church: A Faith-Driven Fundraising Playbook</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>sms for nonprofits</t>
+          <t>giving to the church</t>
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="E112" t="n">
-        <v>21</v>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G112" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>17</v>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5648,28 +5648,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Thank You For Generous Donation: A Practical Guide for Nonprofit Teams</t>
+          <t>Youth Fundraising Ideas For Church: 25+ Real Examples Nonprofits Use</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>thank you for generous donation</t>
+          <t>youth fundraising ideas for church</t>
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="E116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G116" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6811,23 +6811,23 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>religious fundraising ideas</t>
+          <t>raffle prizes</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
         <v>1600</v>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>16</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6849,23 +6849,23 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>raffle prizes</t>
+          <t>religious fundraising ideas</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
         <v>1600</v>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+        <v>26</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7115,23 +7115,23 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>donor databases for nonprofits</t>
+          <t>thank you for your donation</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C32" t="n">
-        <v>46</v>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>17</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -7229,23 +7229,23 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>church donation</t>
+          <t>how to start a fundraiser</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C35" t="n">
-        <v>46</v>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>9</v>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7267,23 +7267,23 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>thank you for your donation</t>
+          <t>basket raffle</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -7305,14 +7305,14 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>how to start a fundraiser</t>
+          <t>fundraising ideas for sports teams</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
@@ -7343,14 +7343,14 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>basket raffle</t>
+          <t>sports fundraising ideas</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -7381,14 +7381,14 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for sports teams</t>
+          <t>how to start a nonprofit organization with no money</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
@@ -7419,14 +7419,14 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>sports fundraising ideas</t>
+          <t>raffle ideas</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C40" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
@@ -7457,14 +7457,14 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>how to start a nonprofit organization with no money</t>
+          <t>how to earn money for a nonprofit organization</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C41" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
@@ -7495,23 +7495,23 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>raffle ideas</t>
+          <t>donor databases for nonprofits</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C42" t="n">
-        <v>19</v>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+        <v>46</v>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -7533,23 +7533,23 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>how to earn money for a nonprofit organization</t>
+          <t>church donation</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
         <v>1300</v>
       </c>
       <c r="C43" t="n">
-        <v>20</v>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+        <v>46</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -7913,23 +7913,23 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>nonprofit websites</t>
+          <t>church fundraising ideas</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="C53" t="n">
-        <v>45</v>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>14</v>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -7951,23 +7951,23 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>church fundraising ideas</t>
+          <t>fundraising ideas for kids</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7989,14 +7989,14 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for kids</t>
+          <t>college nonprofit ideas</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="C55" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
@@ -8027,14 +8027,14 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>college nonprofit ideas</t>
+          <t>raffle prize ideas</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="C56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
@@ -8065,18 +8065,18 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>raffle prize ideas</t>
+          <t>charity event</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="C57" t="n">
-        <v>19</v>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>23</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -8103,14 +8103,14 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>charity event</t>
+          <t>high school fundraising ideas</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="C58" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -8141,14 +8141,14 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>high school fundraising ideas</t>
+          <t>charity gala</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="C59" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
@@ -8179,23 +8179,23 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>charity gala</t>
+          <t>nonprofit websites</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="C60" t="n">
-        <v>26</v>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+        <v>45</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -8597,23 +8597,23 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>tithely app</t>
+          <t>990 forms for nonprofits</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
         <v>880</v>
       </c>
       <c r="C71" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -8635,33 +8635,33 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>990 forms for nonprofits</t>
+          <t>best raffle prizes</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
         <v>880</v>
       </c>
       <c r="C72" t="n">
-        <v>47</v>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>6</v>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -8787,28 +8787,28 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>best raffle prizes</t>
+          <t>tithely app</t>
         </is>
       </c>
       <c r="B76" s="4" t="n">
         <v>880</v>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Ideas</t>
+        <v>46</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -9243,23 +9243,23 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>requesting for donation</t>
+          <t>tithe ly login</t>
         </is>
       </c>
       <c r="B88" s="4" t="n">
         <v>720</v>
       </c>
       <c r="C88" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
@@ -9281,23 +9281,23 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>donation causes</t>
+          <t>church fundraisers</t>
         </is>
       </c>
       <c r="B89" s="4" t="n">
         <v>720</v>
       </c>
       <c r="C89" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9319,14 +9319,14 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>free mass text messaging app</t>
+          <t>requesting for donation</t>
         </is>
       </c>
       <c r="B90" s="4" t="n">
         <v>720</v>
       </c>
       <c r="C90" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
@@ -9357,23 +9357,23 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>tithe ly login</t>
+          <t>donation causes</t>
         </is>
       </c>
       <c r="B91" s="4" t="n">
         <v>720</v>
       </c>
       <c r="C91" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -9395,23 +9395,23 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>church fundraisers</t>
+          <t>free mass text messaging app</t>
         </is>
       </c>
       <c r="B92" s="4" t="n">
         <v>720</v>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E92" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -11295,23 +11295,23 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>non profit company</t>
+          <t>tithely admin login</t>
         </is>
       </c>
       <c r="B142" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C142" t="n">
-        <v>49</v>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E142" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>21</v>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -11333,23 +11333,23 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>tithely admin login</t>
+          <t>companies that donate to nonprofit organizations</t>
         </is>
       </c>
       <c r="B143" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C143" t="n">
-        <v>21</v>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>16</v>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="H143" s="13" t="inlineStr">
@@ -11371,28 +11371,28 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>best church management software</t>
+          <t>free mass text messaging</t>
         </is>
       </c>
       <c r="B144" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C144" t="n">
-        <v>39</v>
-      </c>
-      <c r="D144" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E144" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>20</v>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -11409,18 +11409,18 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>companies that donate to nonprofit organizations</t>
+          <t>how to send a mass text on iphone</t>
         </is>
       </c>
       <c r="B145" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C145" t="n">
-        <v>16</v>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>23</v>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -11447,18 +11447,18 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>free mass text messaging</t>
+          <t>free nonprofit crm</t>
         </is>
       </c>
       <c r="B146" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C146" t="n">
-        <v>20</v>
-      </c>
-      <c r="D146" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>25</v>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
@@ -11485,14 +11485,14 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>how to send a mass text on iphone</t>
+          <t>nonprofit website builder</t>
         </is>
       </c>
       <c r="B147" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C147" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
@@ -11523,14 +11523,14 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>free nonprofit crm</t>
+          <t>credit card processing for nonprofits</t>
         </is>
       </c>
       <c r="B148" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C148" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
@@ -11561,23 +11561,23 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>nonprofit website builder</t>
+          <t>non profit company</t>
         </is>
       </c>
       <c r="B149" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C149" t="n">
-        <v>27</v>
-      </c>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>49</v>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -11599,28 +11599,28 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>credit card processing for nonprofits</t>
+          <t>best church management software</t>
         </is>
       </c>
       <c r="B150" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C150" t="n">
-        <v>28</v>
-      </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E150" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>39</v>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13043,23 +13043,23 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>sample thank you note for donation</t>
+          <t>donation x</t>
         </is>
       </c>
       <c r="B188" s="4" t="n">
         <v>390</v>
       </c>
       <c r="C188" t="n">
-        <v>34</v>
-      </c>
-      <c r="D188" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E188" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>13</v>
+      </c>
+      <c r="D188" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E188" s="9" t="inlineStr">
+        <is>
+          <t>Mobile Fundraising</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="H188" s="13" t="inlineStr">
@@ -13081,23 +13081,23 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>free church tithe and offering software</t>
+          <t>sample thank you note for donation</t>
         </is>
       </c>
       <c r="B189" s="4" t="n">
         <v>390</v>
       </c>
       <c r="C189" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E189" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="E189" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="H189" s="13" t="inlineStr">
@@ -13119,23 +13119,23 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>donation x</t>
+          <t>free church tithe and offering software</t>
         </is>
       </c>
       <c r="B190" s="4" t="n">
         <v>390</v>
       </c>
       <c r="C190" t="n">
-        <v>13</v>
-      </c>
-      <c r="D190" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E190" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Fundraising</t>
+        <v>25</v>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -17185,14 +17185,14 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>crm systems for political campaigns</t>
+          <t>mass texting service for nonprofits</t>
         </is>
       </c>
       <c r="B297" s="4" t="n">
         <v>260</v>
       </c>
       <c r="C297" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D297" s="10" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="H297" s="13" t="inlineStr">
@@ -17223,18 +17223,18 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>mass texting service for nonprofits</t>
+          <t>campaign text</t>
         </is>
       </c>
       <c r="B298" s="4" t="n">
         <v>260</v>
       </c>
       <c r="C298" t="n">
-        <v>17</v>
-      </c>
-      <c r="D298" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>24</v>
+      </c>
+      <c r="D298" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E298" s="12" t="inlineStr">
@@ -17261,14 +17261,14 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>campaign text</t>
+          <t>nonprofit conferences</t>
         </is>
       </c>
       <c r="B299" s="4" t="n">
         <v>260</v>
       </c>
       <c r="C299" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D299" s="7" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="H299" s="13" t="inlineStr">
@@ -17299,23 +17299,23 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>nonprofit conferences</t>
+          <t>church texting</t>
         </is>
       </c>
       <c r="B300" s="4" t="n">
         <v>260</v>
       </c>
       <c r="C300" t="n">
-        <v>28</v>
-      </c>
-      <c r="D300" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E300" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>19</v>
+      </c>
+      <c r="D300" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E300" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -17337,23 +17337,23 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>messaging platform</t>
+          <t>fundraising ideas for church building</t>
         </is>
       </c>
       <c r="B301" s="4" t="n">
         <v>260</v>
       </c>
       <c r="C301" t="n">
-        <v>37</v>
-      </c>
-      <c r="D301" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E301" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>20</v>
+      </c>
+      <c r="D301" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E301" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -17375,23 +17375,23 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>church texting</t>
+          <t>crm systems for political campaigns</t>
         </is>
       </c>
       <c r="B302" s="4" t="n">
         <v>260</v>
       </c>
       <c r="C302" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D302" s="10" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E302" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+      <c r="E302" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -17413,23 +17413,23 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>fundraising ideas for church building</t>
+          <t>messaging platform</t>
         </is>
       </c>
       <c r="B303" s="4" t="n">
         <v>260</v>
       </c>
       <c r="C303" t="n">
-        <v>20</v>
-      </c>
-      <c r="D303" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E303" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>37</v>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E303" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -24329,23 +24329,23 @@
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
         <is>
-          <t>youth fundraising ideas for church</t>
+          <t>sms for nonprofits</t>
         </is>
       </c>
       <c r="B485" s="4" t="n">
         <v>170</v>
       </c>
       <c r="C485" t="n">
-        <v>10</v>
-      </c>
-      <c r="D485" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E485" s="11" t="inlineStr">
-        <is>
-          <t>Church Fundraising</t>
+        <v>21</v>
+      </c>
+      <c r="D485" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E485" s="12" t="inlineStr">
+        <is>
+          <t>Nonprofit Texting</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -24367,14 +24367,14 @@
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
         <is>
-          <t>sms for nonprofits</t>
+          <t>text messaging service for nonprofits</t>
         </is>
       </c>
       <c r="B486" s="4" t="n">
         <v>170</v>
       </c>
       <c r="C486" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D486" s="7" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
         <is>
-          <t>text messaging service for nonprofits</t>
+          <t>political text messaging service</t>
         </is>
       </c>
       <c r="B487" s="4" t="n">
@@ -24443,7 +24443,7 @@
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
         <is>
-          <t>political text messaging service</t>
+          <t>text marketing campaigns</t>
         </is>
       </c>
       <c r="B488" s="4" t="n">
@@ -24481,23 +24481,23 @@
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
         <is>
-          <t>text marketing campaigns</t>
+          <t>youth fundraising ideas for church</t>
         </is>
       </c>
       <c r="B489" s="4" t="n">
         <v>170</v>
       </c>
       <c r="C489" t="n">
-        <v>23</v>
-      </c>
-      <c r="D489" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E489" s="12" t="inlineStr">
-        <is>
-          <t>Nonprofit Texting</t>
+        <v>10</v>
+      </c>
+      <c r="D489" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E489" s="11" t="inlineStr">
+        <is>
+          <t>Church Fundraising</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
